--- a/data/sports/dota2/research.xlsx
+++ b/data/sports/dota2/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ145" headerRowCount="1">
-  <autoFilter ref="A1:DQ145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ148" headerRowCount="1">
+  <autoFilter ref="A1:DQ148"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$145)</f>
+        <f>COUNTA('Picks'!$A$2:$A$148)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$145,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$148,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$145,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")+COUNTIFS('Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")+COUNTIFS('Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$145,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$148,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"win")/(COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"win")+COUNTIFS('Picks'!$BX$2:$BX$145,"&gt;0",'Picks'!$V$2:$V$145,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"win")/(COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"win")+COUNTIFS('Picks'!$BX$2:$BX$148,"&gt;0",'Picks'!$V$2:$V$148,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$145)/SUM('Picks'!$BX$2:$BX$145),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$148)/SUM('Picks'!$BX$2:$BX$148),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$145)</f>
+        <f>SUM('Picks'!$BY$2:$BY$148)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$145,"&lt;&gt;",'Picks'!$AB$2:$AB$145),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$148,"&lt;&gt;",'Picks'!$AB$2:$AB$148),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$145,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$145,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$148,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$145,'Picks'!$AM$2:$AM$145,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$148,'Picks'!$AM$2:$AM$148,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$145,'Picks'!$H$2:$H$145,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$148,'Picks'!$H$2:$H$148,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$145,'Picks'!$H$2:$H$145,$A14,'Picks'!$U$2:$U$145,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$148,'Picks'!$H$2:$H$148,$A14,'Picks'!$U$2:$U$148,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$145,'Picks'!$H$2:$H$145,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$148,'Picks'!$H$2:$H$148,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$145,'Picks'!$H$2:$H$145,$A15,'Picks'!$U$2:$U$145,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$148,'Picks'!$H$2:$H$148,$A15,'Picks'!$U$2:$U$148,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled",'Picks'!$V$2:$V$145,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled",'Picks'!$V$2:$V$148,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$145,'Picks'!$H$2:$H$145,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$148,'Picks'!$H$2:$H$148,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$145,'Picks'!$H$2:$H$145,$A16,'Picks'!$U$2:$U$145,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$148,'Picks'!$H$2:$H$148,$A16,'Picks'!$U$2:$U$148,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ145"/>
+  <dimension ref="A1:DQ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -46949,18 +46949,38 @@
       </c>
       <c r="U143" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V143" s="24" t="n"/>
-      <c r="W143" s="26" t="n"/>
-      <c r="X143" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W143" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X143" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y143" s="25" t="n"/>
-      <c r="Z143" s="26" t="n"/>
-      <c r="AA143" s="28" t="n"/>
-      <c r="AB143" s="28" t="n"/>
-      <c r="AC143" s="30" t="n"/>
-      <c r="AD143" s="24" t="n"/>
+      <c r="Z143" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="AA143" s="28" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AB143" s="28" t="n">
+        <v>-0.000815</v>
+      </c>
+      <c r="AC143" s="30" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="AD143" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T10:01:10.196234Z</t>
+        </is>
+      </c>
       <c r="AE143" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-yg-iac-2026-10-06).</t>
@@ -47103,8 +47123,12 @@
       <c r="BN143" s="28" t="n"/>
       <c r="BO143" s="28" t="n"/>
       <c r="BP143" s="25" t="n"/>
-      <c r="BQ143" s="27" t="n"/>
-      <c r="BR143" s="28" t="n"/>
+      <c r="BQ143" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BR143" s="28" t="n">
+        <v>0.57</v>
+      </c>
       <c r="BS143" s="28" t="n"/>
       <c r="BT143" s="28" t="n"/>
       <c r="BU143" s="25" t="n"/>
@@ -47246,18 +47270,38 @@
       </c>
       <c r="U144" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V144" s="24" t="n"/>
-      <c r="W144" s="26" t="n"/>
-      <c r="X144" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V144" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W144" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X144" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y144" s="25" t="n"/>
-      <c r="Z144" s="26" t="n"/>
-      <c r="AA144" s="28" t="n"/>
-      <c r="AB144" s="28" t="n"/>
-      <c r="AC144" s="30" t="n"/>
-      <c r="AD144" s="24" t="n"/>
+      <c r="Z144" s="26" t="n">
+        <v>-900</v>
+      </c>
+      <c r="AA144" s="28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB144" s="28" t="n">
+        <v>0.309836</v>
+      </c>
+      <c r="AC144" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD144" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:02:46.753236Z</t>
+        </is>
+      </c>
       <c r="AE144" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5900 (market_slug=aec-dota2-hul-ch-2026-10-06).</t>
@@ -47270,7 +47314,7 @@
       </c>
       <c r="AG144" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH144" s="24" t="n"/>
@@ -47400,8 +47444,12 @@
       <c r="BN144" s="28" t="n"/>
       <c r="BO144" s="28" t="n"/>
       <c r="BP144" s="25" t="n"/>
-      <c r="BQ144" s="27" t="n"/>
-      <c r="BR144" s="28" t="n"/>
+      <c r="BQ144" s="27" t="n">
+        <v>1.111111</v>
+      </c>
+      <c r="BR144" s="28" t="n">
+        <v>0.9</v>
+      </c>
       <c r="BS144" s="28" t="n"/>
       <c r="BT144" s="28" t="n"/>
       <c r="BU144" s="25" t="n"/>
@@ -47465,12 +47513,12 @@
     <row r="145" ht="36" customHeight="1">
       <c r="A145" s="24" t="inlineStr">
         <is>
-          <t>9eb76bd46df640bb</t>
+          <t>6084828cb57b4b7c</t>
         </is>
       </c>
       <c r="B145" s="24" t="inlineStr">
         <is>
-          <t>2026-10-05T22:25:55.486296Z</t>
+          <t>2026-10-06T10:51:23.725681Z</t>
         </is>
       </c>
       <c r="C145" s="24" t="inlineStr">
@@ -47524,11 +47572,11 @@
         <v>0.45045</v>
       </c>
       <c r="O145" s="28" t="n">
-        <v>0.587048</v>
+        <v>0.586581</v>
       </c>
       <c r="P145" s="28" t="n"/>
       <c r="Q145" s="28" t="n">
-        <v>0.136598</v>
+        <v>0.136131</v>
       </c>
       <c r="R145" s="26" t="n">
         <v>88</v>
@@ -47543,18 +47591,38 @@
       </c>
       <c r="U145" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V145" s="24" t="n"/>
-      <c r="W145" s="26" t="n"/>
-      <c r="X145" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V145" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W145" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y145" s="25" t="n"/>
-      <c r="Z145" s="26" t="n"/>
-      <c r="AA145" s="28" t="n"/>
-      <c r="AB145" s="28" t="n"/>
-      <c r="AC145" s="30" t="n"/>
-      <c r="AD145" s="24" t="n"/>
+      <c r="Z145" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA145" s="28" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB145" s="28" t="n">
+        <v>-0.00045</v>
+      </c>
+      <c r="AC145" s="30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD145" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:02:46.998047Z</t>
+        </is>
+      </c>
       <c r="AE145" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-tsea-yes-2026-10-06).</t>
@@ -47641,7 +47709,7 @@
       </c>
       <c r="BA145" s="24" t="inlineStr">
         <is>
-          <t>8fd316347e24d5faa7a92e7ef89a639c490973a25d2b8dbb2af706a2af5abf92</t>
+          <t>6759e71c6db4f5d9b0ec78bb2474758963eb5552e8a6657a0edf8ae49f26fe3d</t>
         </is>
       </c>
       <c r="BB145" s="24" t="inlineStr">
@@ -47656,7 +47724,7 @@
       </c>
       <c r="BD145" s="24" t="inlineStr">
         <is>
-          <t>8fd316347e24d5faa7a92e7ef89a639c490973a25d2b8dbb2af706a2af5abf92</t>
+          <t>6759e71c6db4f5d9b0ec78bb2474758963eb5552e8a6657a0edf8ae49f26fe3d</t>
         </is>
       </c>
       <c r="BE145" s="24" t="inlineStr">
@@ -47676,7 +47744,7 @@
       </c>
       <c r="BH145" s="24" t="inlineStr">
         <is>
-          <t>2026-10-05T22:25:44.939151Z</t>
+          <t>2026-10-06T10:51:03.361802Z</t>
         </is>
       </c>
       <c r="BI145" s="24" t="inlineStr">
@@ -47697,8 +47765,12 @@
       <c r="BN145" s="28" t="n"/>
       <c r="BO145" s="28" t="n"/>
       <c r="BP145" s="25" t="n"/>
-      <c r="BQ145" s="27" t="n"/>
-      <c r="BR145" s="28" t="n"/>
+      <c r="BQ145" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BR145" s="28" t="n">
+        <v>0.45</v>
+      </c>
       <c r="BS145" s="28" t="n"/>
       <c r="BT145" s="28" t="n"/>
       <c r="BU145" s="25" t="n"/>
@@ -47755,7 +47827,922 @@
       <c r="DP145" s="24" t="n"/>
       <c r="DQ145" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "8fd316347e24d5faa7a92e7ef89a639c490973a25d2b8dbb2af706a2af5abf92", "away_team": "Yellow Submarine", "event_id": "143565", "event_start_utc": "2026-10-06T14:00:00Z", "features": {"away_elo": 1786.068317, "away_history_count": 285, "home_elo": 1855.48017, "home_history_count": 23}, "historical_source_observation_times_verified": false, "home_team": "Team Synapse", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 285, "bo3:4:25201": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-05T11:10:00Z", "bo3:4:25201": "2026-10-05T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.08103315066152637, "platt_slope": 0.8449481325411426, "ratings": {"bo3:4:16486": 1786.068317, "bo3:4:25201": 1855.48017}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-05T22:25:23.694580+00:00", "team_ids": ["bo3:4:25201", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-05T22:25:23.694580+00:00", "probabilities": {"away": 0.412952, "home": 0.587048}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "de1d70f15f33b8dcda068e21a4a94c374808390850c2e0df4df0409544cc1b27", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "6759e71c6db4f5d9b0ec78bb2474758963eb5552e8a6657a0edf8ae49f26fe3d", "away_team": "Yellow Submarine", "event_id": "143565", "event_start_utc": "2026-10-06T14:00:00Z", "features": {"away_elo": 1786.028424, "away_history_count": 285, "home_elo": 1855.458017, "home_history_count": 23}, "historical_source_observation_times_verified": false, "home_team": "Team Synapse", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 285, "bo3:4:25201": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-05T11:10:00Z", "bo3:4:25201": "2026-10-05T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0806649303548175, "platt_slope": 0.8439015098774778, "ratings": {"bo3:4:16486": 1786.028424, "bo3:4:25201": 1855.458017}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T10:50:53.111088+00:00", "team_ids": ["bo3:4:25201", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T10:50:53.111088+00:00", "probabilities": {"away": 0.413419, "home": 0.586581}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2d95927cb9101c0d665d6d64969b5ac62cd066f6a48af941c35e0f56d54aa876", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="36" customHeight="1">
+      <c r="A146" s="24" t="inlineStr">
+        <is>
+          <t>dfcb0d3ca334487c</t>
+        </is>
+      </c>
+      <c r="B146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:34:32.687894Z</t>
+        </is>
+      </c>
+      <c r="C146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D146" s="24" t="inlineStr">
+        <is>
+          <t>144500</t>
+        </is>
+      </c>
+      <c r="E146" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F146" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="G146" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="H146" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I146" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J146" s="25" t="n"/>
+      <c r="K146" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L146" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M146" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N146" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O146" s="28" t="n">
+        <v>0.552316</v>
+      </c>
+      <c r="P146" s="28" t="n"/>
+      <c r="Q146" s="28" t="n">
+        <v>0.013145</v>
+      </c>
+      <c r="R146" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S146" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T146" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U146" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V146" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W146" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y146" s="25" t="n"/>
+      <c r="Z146" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA146" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB146" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC146" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:02:49.440470Z</t>
+        </is>
+      </c>
+      <c r="AE146" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-dota2-leg-mouz-2026-10-06).</t>
+        </is>
+      </c>
+      <c r="AF146" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG146" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH146" s="24" t="n"/>
+      <c r="AI146" s="31" t="n"/>
+      <c r="AJ146" s="31" t="n"/>
+      <c r="AK146" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL146" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM146" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN146" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO146" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP146" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AQ146" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AR146" s="24" t="inlineStr">
+        <is>
+          <t>MOUZ</t>
+        </is>
+      </c>
+      <c r="AS146" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AT146" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AU146" s="24" t="inlineStr">
+        <is>
+          <t>LEGION</t>
+        </is>
+      </c>
+      <c r="AV146" s="24" t="n"/>
+      <c r="AW146" s="24" t="n"/>
+      <c r="AX146" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY146" s="24" t="n"/>
+      <c r="AZ146" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA146" s="24" t="inlineStr">
+        <is>
+          <t>4690b99c58f0ec38c0a7f8871260c2693630b47ca56007141cc547de632674ee</t>
+        </is>
+      </c>
+      <c r="BB146" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC146" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD146" s="24" t="inlineStr">
+        <is>
+          <t>4690b99c58f0ec38c0a7f8871260c2693630b47ca56007141cc547de632674ee</t>
+        </is>
+      </c>
+      <c r="BE146" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF146" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG146" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH146" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:34:12.398493Z</t>
+        </is>
+      </c>
+      <c r="BI146" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ146" s="25" t="n"/>
+      <c r="BK146" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL146" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM146" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN146" s="28" t="n"/>
+      <c r="BO146" s="28" t="n"/>
+      <c r="BP146" s="25" t="n"/>
+      <c r="BQ146" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR146" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS146" s="28" t="n"/>
+      <c r="BT146" s="28" t="n"/>
+      <c r="BU146" s="25" t="n"/>
+      <c r="BV146" s="29" t="n"/>
+      <c r="BW146" s="24" t="n"/>
+      <c r="BX146" s="30" t="n"/>
+      <c r="BY146" s="27" t="n"/>
+      <c r="BZ146" s="24" t="n"/>
+      <c r="CA146" s="31" t="n"/>
+      <c r="CB146" s="24" t="n"/>
+      <c r="CC146" s="24" t="n"/>
+      <c r="CD146" s="24" t="n"/>
+      <c r="CE146" s="24" t="n"/>
+      <c r="CF146" s="24" t="n"/>
+      <c r="CG146" s="24" t="n"/>
+      <c r="CH146" s="24" t="n"/>
+      <c r="CI146" s="24" t="n"/>
+      <c r="CJ146" s="24" t="n"/>
+      <c r="CK146" s="24" t="n"/>
+      <c r="CL146" s="24" t="n"/>
+      <c r="CM146" s="24" t="n"/>
+      <c r="CN146" s="24" t="n"/>
+      <c r="CO146" s="24" t="n"/>
+      <c r="CP146" s="24" t="n"/>
+      <c r="CQ146" s="24" t="n"/>
+      <c r="CR146" s="24" t="n"/>
+      <c r="CS146" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT146" s="24" t="n"/>
+      <c r="CU146" s="24" t="n"/>
+      <c r="CV146" s="24" t="n"/>
+      <c r="CW146" s="24" t="n"/>
+      <c r="CX146" s="24" t="n"/>
+      <c r="CY146" s="24" t="n"/>
+      <c r="CZ146" s="24" t="n"/>
+      <c r="DA146" s="24" t="n"/>
+      <c r="DB146" s="24" t="n"/>
+      <c r="DC146" s="24" t="n"/>
+      <c r="DD146" s="24" t="n"/>
+      <c r="DE146" s="24" t="n"/>
+      <c r="DF146" s="24" t="n"/>
+      <c r="DG146" s="24" t="n"/>
+      <c r="DH146" s="24" t="n"/>
+      <c r="DI146" s="24" t="n"/>
+      <c r="DJ146" s="24" t="n"/>
+      <c r="DK146" s="24" t="n"/>
+      <c r="DL146" s="24" t="n"/>
+      <c r="DM146" s="24" t="n"/>
+      <c r="DN146" s="24" t="n"/>
+      <c r="DO146" s="24" t="n"/>
+      <c r="DP146" s="24" t="n"/>
+      <c r="DQ146" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4690b99c58f0ec38c0a7f8871260c2693630b47ca56007141cc547de632674ee", "away_team": "MOUZ", "event_id": "144500", "event_start_utc": "2026-10-06T17:00:00Z", "features": {"away_elo": 1644.197963, "away_history_count": 363, "home_elo": 1532.76, "home_history_count": 1}, "historical_source_observation_times_verified": false, "home_team": "LEGION", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15032": 363, "bo3:4:25401": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15032": "2026-10-05T18:00:00Z", "bo3:4:25401": "2026-10-05T14:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.08111949537955908, "platt_slope": 0.8418535477548365, "ratings": {"bo3:4:15032": 1644.197963, "bo3:4:25401": 1532.76}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T16:34:12.325280+00:00", "team_ids": ["bo3:4:25401", "bo3:4:15032"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T16:34:12.325280+00:00", "probabilities": {"away": 0.552316, "home": 0.447684}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d7ab51a4f880e3c1e54ff9e61bc180831b900208cf5f6dcb73682f2580b1dd3d", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="36" customHeight="1">
+      <c r="A147" s="24" t="inlineStr">
+        <is>
+          <t>dc9dc5e2c86f41bb</t>
+        </is>
+      </c>
+      <c r="B147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:56.390271Z</t>
+        </is>
+      </c>
+      <c r="C147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T03:00:00Z</t>
+        </is>
+      </c>
+      <c r="D147" s="24" t="inlineStr">
+        <is>
+          <t>145226</t>
+        </is>
+      </c>
+      <c r="E147" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F147" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="G147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="H147" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I147" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J147" s="25" t="n"/>
+      <c r="K147" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L147" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M147" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N147" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O147" s="28" t="n">
+        <v>0.550796</v>
+      </c>
+      <c r="P147" s="28" t="n"/>
+      <c r="Q147" s="28" t="n">
+        <v>-0.148904</v>
+      </c>
+      <c r="R147" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T147" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U147" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V147" s="24" t="n"/>
+      <c r="W147" s="26" t="n"/>
+      <c r="X147" s="26" t="n"/>
+      <c r="Y147" s="25" t="n"/>
+      <c r="Z147" s="26" t="n"/>
+      <c r="AA147" s="28" t="n"/>
+      <c r="AB147" s="28" t="n"/>
+      <c r="AC147" s="30" t="n"/>
+      <c r="AD147" s="24" t="n"/>
+      <c r="AE147" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-db-y123-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF147" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG147" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH147" s="24" t="n"/>
+      <c r="AI147" s="31" t="n"/>
+      <c r="AJ147" s="31" t="n"/>
+      <c r="AK147" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL147" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM147" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN147" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO147" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP147" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="AQ147" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="AR147" s="24" t="inlineStr">
+        <is>
+          <t>ЯЧЁ123</t>
+        </is>
+      </c>
+      <c r="AS147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AT147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AU147" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AV147" s="24" t="n"/>
+      <c r="AW147" s="24" t="n"/>
+      <c r="AX147" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY147" s="24" t="n"/>
+      <c r="AZ147" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA147" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BB147" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC147" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD147" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BE147" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF147" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG147" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH147" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:25.556351Z</t>
+        </is>
+      </c>
+      <c r="BI147" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ147" s="25" t="n"/>
+      <c r="BK147" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL147" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM147" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN147" s="28" t="n"/>
+      <c r="BO147" s="28" t="n"/>
+      <c r="BP147" s="25" t="n"/>
+      <c r="BQ147" s="27" t="n"/>
+      <c r="BR147" s="28" t="n"/>
+      <c r="BS147" s="28" t="n"/>
+      <c r="BT147" s="28" t="n"/>
+      <c r="BU147" s="25" t="n"/>
+      <c r="BV147" s="29" t="n"/>
+      <c r="BW147" s="24" t="n"/>
+      <c r="BX147" s="30" t="n"/>
+      <c r="BY147" s="27" t="n"/>
+      <c r="BZ147" s="24" t="n"/>
+      <c r="CA147" s="31" t="n"/>
+      <c r="CB147" s="24" t="n"/>
+      <c r="CC147" s="24" t="n"/>
+      <c r="CD147" s="24" t="n"/>
+      <c r="CE147" s="24" t="n"/>
+      <c r="CF147" s="24" t="n"/>
+      <c r="CG147" s="24" t="n"/>
+      <c r="CH147" s="24" t="n"/>
+      <c r="CI147" s="24" t="n"/>
+      <c r="CJ147" s="24" t="n"/>
+      <c r="CK147" s="24" t="n"/>
+      <c r="CL147" s="24" t="n"/>
+      <c r="CM147" s="24" t="n"/>
+      <c r="CN147" s="24" t="n"/>
+      <c r="CO147" s="24" t="n"/>
+      <c r="CP147" s="24" t="n"/>
+      <c r="CQ147" s="24" t="n"/>
+      <c r="CR147" s="24" t="n"/>
+      <c r="CS147" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT147" s="24" t="n"/>
+      <c r="CU147" s="24" t="n"/>
+      <c r="CV147" s="24" t="n"/>
+      <c r="CW147" s="24" t="n"/>
+      <c r="CX147" s="24" t="n"/>
+      <c r="CY147" s="24" t="n"/>
+      <c r="CZ147" s="24" t="n"/>
+      <c r="DA147" s="24" t="n"/>
+      <c r="DB147" s="24" t="n"/>
+      <c r="DC147" s="24" t="n"/>
+      <c r="DD147" s="24" t="n"/>
+      <c r="DE147" s="24" t="n"/>
+      <c r="DF147" s="24" t="n"/>
+      <c r="DG147" s="24" t="n"/>
+      <c r="DH147" s="24" t="n"/>
+      <c r="DI147" s="24" t="n"/>
+      <c r="DJ147" s="24" t="n"/>
+      <c r="DK147" s="24" t="n"/>
+      <c r="DL147" s="24" t="n"/>
+      <c r="DM147" s="24" t="n"/>
+      <c r="DN147" s="24" t="n"/>
+      <c r="DO147" s="24" t="n"/>
+      <c r="DP147" s="24" t="n"/>
+      <c r="DQ147" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642", "away_team": "\u042f\u0427\u0401123", "event_id": "145226", "event_start_utc": "2026-10-07T03:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1584.551416, "home_history_count": 37}, "historical_source_observation_times_verified": false, "home_team": "Direborn", "inference_inputs": {"book_state": {"games_played": {"bo3:4:24344": 37}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:24344": "2026-10-06T06:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07646024717646603, "platt_slope": 0.8471774676108041, "ratings": {"bo3:4:24344": 1584.551416}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.483347+00:00", "team_ids": ["bo3:4:24344", "unknown:\u044f\u0447\u0435123"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.483347+00:00", "probabilities": {"away": 0.449204, "home": 0.550796}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "dc330291efd584143729f621ac5b58f7d873a090a9b0f169c927e0ebb9493b25", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="36" customHeight="1">
+      <c r="A148" s="24" t="inlineStr">
+        <is>
+          <t>380c7106e0754118</t>
+        </is>
+      </c>
+      <c r="B148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:56.390271Z</t>
+        </is>
+      </c>
+      <c r="C148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D148" s="24" t="inlineStr">
+        <is>
+          <t>145796</t>
+        </is>
+      </c>
+      <c r="E148" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F148" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="G148" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="H148" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I148" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J148" s="25" t="n"/>
+      <c r="K148" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L148" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M148" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N148" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O148" s="28" t="n">
+        <v>0.640253</v>
+      </c>
+      <c r="P148" s="28" t="n"/>
+      <c r="Q148" s="28" t="n">
+        <v>0.030878</v>
+      </c>
+      <c r="R148" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="S148" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T148" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U148" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V148" s="24" t="n"/>
+      <c r="W148" s="26" t="n"/>
+      <c r="X148" s="26" t="n"/>
+      <c r="Y148" s="25" t="n"/>
+      <c r="Z148" s="26" t="n"/>
+      <c r="AA148" s="28" t="n"/>
+      <c r="AB148" s="28" t="n"/>
+      <c r="AC148" s="30" t="n"/>
+      <c r="AD148" s="24" t="n"/>
+      <c r="AE148" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-bbl-yes-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF148" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG148" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH148" s="24" t="n"/>
+      <c r="AI148" s="31" t="n"/>
+      <c r="AJ148" s="31" t="n"/>
+      <c r="AK148" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL148" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM148" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN148" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO148" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP148" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AQ148" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AR148" s="24" t="inlineStr">
+        <is>
+          <t>Yellow Submarine</t>
+        </is>
+      </c>
+      <c r="AS148" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AT148" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AU148" s="24" t="inlineStr">
+        <is>
+          <t>Blasterbl</t>
+        </is>
+      </c>
+      <c r="AV148" s="24" t="n"/>
+      <c r="AW148" s="24" t="n"/>
+      <c r="AX148" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY148" s="24" t="n"/>
+      <c r="AZ148" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA148" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BB148" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC148" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD148" s="24" t="inlineStr">
+        <is>
+          <t>c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642</t>
+        </is>
+      </c>
+      <c r="BE148" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF148" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG148" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH148" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:25.683597Z</t>
+        </is>
+      </c>
+      <c r="BI148" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ148" s="25" t="n"/>
+      <c r="BK148" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL148" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM148" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN148" s="28" t="n"/>
+      <c r="BO148" s="28" t="n"/>
+      <c r="BP148" s="25" t="n"/>
+      <c r="BQ148" s="27" t="n"/>
+      <c r="BR148" s="28" t="n"/>
+      <c r="BS148" s="28" t="n"/>
+      <c r="BT148" s="28" t="n"/>
+      <c r="BU148" s="25" t="n"/>
+      <c r="BV148" s="29" t="n"/>
+      <c r="BW148" s="24" t="n"/>
+      <c r="BX148" s="30" t="n"/>
+      <c r="BY148" s="27" t="n"/>
+      <c r="BZ148" s="24" t="n"/>
+      <c r="CA148" s="31" t="n"/>
+      <c r="CB148" s="24" t="n"/>
+      <c r="CC148" s="24" t="n"/>
+      <c r="CD148" s="24" t="n"/>
+      <c r="CE148" s="24" t="n"/>
+      <c r="CF148" s="24" t="n"/>
+      <c r="CG148" s="24" t="n"/>
+      <c r="CH148" s="24" t="n"/>
+      <c r="CI148" s="24" t="n"/>
+      <c r="CJ148" s="24" t="n"/>
+      <c r="CK148" s="24" t="n"/>
+      <c r="CL148" s="24" t="n"/>
+      <c r="CM148" s="24" t="n"/>
+      <c r="CN148" s="24" t="n"/>
+      <c r="CO148" s="24" t="n"/>
+      <c r="CP148" s="24" t="n"/>
+      <c r="CQ148" s="24" t="n"/>
+      <c r="CR148" s="24" t="n"/>
+      <c r="CS148" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT148" s="24" t="n"/>
+      <c r="CU148" s="24" t="n"/>
+      <c r="CV148" s="24" t="n"/>
+      <c r="CW148" s="24" t="n"/>
+      <c r="CX148" s="24" t="n"/>
+      <c r="CY148" s="24" t="n"/>
+      <c r="CZ148" s="24" t="n"/>
+      <c r="DA148" s="24" t="n"/>
+      <c r="DB148" s="24" t="n"/>
+      <c r="DC148" s="24" t="n"/>
+      <c r="DD148" s="24" t="n"/>
+      <c r="DE148" s="24" t="n"/>
+      <c r="DF148" s="24" t="n"/>
+      <c r="DG148" s="24" t="n"/>
+      <c r="DH148" s="24" t="n"/>
+      <c r="DI148" s="24" t="n"/>
+      <c r="DJ148" s="24" t="n"/>
+      <c r="DK148" s="24" t="n"/>
+      <c r="DL148" s="24" t="n"/>
+      <c r="DM148" s="24" t="n"/>
+      <c r="DN148" s="24" t="n"/>
+      <c r="DO148" s="24" t="n"/>
+      <c r="DP148" s="24" t="n"/>
+      <c r="DQ148" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "c6996bf486b3088429204679c4a6b5d24c63cbcf4cadb3e51613f46a7fcb8642", "away_team": "Yellow Submarine", "event_id": "145796", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1759.660919, "away_history_count": 286, "home_elo": 1497.898695, "home_history_count": 2}, "historical_source_observation_times_verified": false, "home_team": "Blasterbl", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16486": 286, "bo3:4:23832": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16486": "2026-10-06T14:35:00Z", "bo3:4:23832": "2026-10-06T12:20:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07646024717646603, "platt_slope": 0.8471774676108041, "ratings": {"bo3:4:16486": 1759.660919, "bo3:4:23832": 1497.898695}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.483347+00:00", "team_ids": ["bo3:4:23832", "bo3:4:16486"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.483347+00:00", "probabilities": {"away": 0.640253, "home": 0.359747}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "72c0f4514c8da658b54751da2293583b1dca94c0c2906e7fcb514d3472bc5bc3", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/dota2/research.xlsx
+++ b/data/sports/dota2/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ28" headerRowCount="1">
-  <autoFilter ref="A1:DQ28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ31" headerRowCount="1">
+  <autoFilter ref="A1:DQ31"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$28)</f>
+        <f>COUNTA('Picks'!$A$2:$A$31)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$28,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$28,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")/(COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"win")+COUNTIFS('Picks'!$BX$2:$BX$28,"&gt;0",'Picks'!$V$2:$V$28,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$28)/SUM('Picks'!$BX$2:$BX$28),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$28)</f>
+        <f>SUM('Picks'!$BY$2:$BY$31)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$28,"&lt;&gt;",'Picks'!$AB$2:$AB$28),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$28,'Picks'!$AM$2:$AM$28,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A14,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A15,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled",'Picks'!$V$2:$V$28,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$28,'Picks'!$H$2:$H$28,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$28,'Picks'!$H$2:$H$28,$A16,'Picks'!$U$2:$U$28,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ28"/>
+  <dimension ref="A1:DQ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9432,12 +9432,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="24" t="inlineStr">
         <is>
-          <t>55c35ff24a874217</t>
+          <t>6feed3de3f9b4f25</t>
         </is>
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:54.449023Z</t>
+          <t>2026-10-14T05:58:58.433878Z</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -9467,45 +9467,47 @@
       </c>
       <c r="H26" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>total</t>
         </is>
       </c>
       <c r="I26" s="24" t="inlineStr">
         <is>
-          <t>away</t>
-        </is>
-      </c>
-      <c r="J26" s="25" t="n"/>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L26" s="26" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.75188</v>
       </c>
       <c r="N26" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.570815</v>
       </c>
       <c r="O26" s="28" t="n">
-        <v>0.591647</v>
+        <v>0.507493</v>
       </c>
       <c r="P26" s="28" t="n"/>
       <c r="Q26" s="28" t="n">
-        <v>-0.037983</v>
+        <v>-0.063322</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" s="29" t="n">
         <v>1</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v6</t>
+          <t>dota2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U26" s="24" t="inlineStr">
@@ -9524,7 +9526,7 @@
       <c r="AD26" s="24" t="n"/>
       <c r="AE26" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-dota2-nemiga-kalmy-2026-10-14-tot-2pt5).</t>
         </is>
       </c>
       <c r="AF26" s="31" t="inlineStr">
@@ -9608,7 +9610,7 @@
       </c>
       <c r="BA26" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BB26" s="24" t="inlineStr">
@@ -9618,12 +9620,12 @@
       </c>
       <c r="BC26" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v6</t>
+          <t>dota2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD26" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BE26" s="24" t="inlineStr">
@@ -9638,12 +9640,12 @@
       </c>
       <c r="BG26" s="24" t="inlineStr">
         <is>
-          <t>dota2-tiered-elo-v6</t>
+          <t>dota2-total-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH26" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:29:58.800963Z</t>
+          <t>2026-10-14T05:52:44.375366Z</t>
         </is>
       </c>
       <c r="BI26" s="24" t="inlineStr">
@@ -9651,15 +9653,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="25" t="n">
+        <v>2.5</v>
+      </c>
       <c r="BK26" s="26" t="n">
-        <v>-170</v>
+        <v>-133</v>
       </c>
       <c r="BL26" s="27" t="n">
-        <v>1.588235</v>
+        <v>1.75188</v>
       </c>
       <c r="BM26" s="28" t="n">
-        <v>0.62963</v>
+        <v>0.570815</v>
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
@@ -9720,31 +9724,27 @@
       <c r="DN26" s="24" t="n"/>
       <c r="DO26" s="24" t="n"/>
       <c r="DP26" s="24" t="n"/>
-      <c r="DQ26" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "Kalmychata", "event_id": "158214", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1592.500579, "away_history_count": 168, "home_elo": 1488.072875, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15089": 168, "bo3:4:16398": 297}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15089": "2026-10-13T09:00:00Z", "bo3:4:16398": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:15089": 1592.500579, "bo3:4:16398": 1488.072875}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:16398", "bo3:4:15089"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.591647, "home": 0.408353}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2685a146ca3f8bb6364c69a072fbde4add522d53bd902c0ee0b3c9209ae30f73", "sport": "DOTA2"}</t>
-        </is>
-      </c>
+      <c r="DQ26" s="24" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="24" t="inlineStr">
         <is>
-          <t>d792a57d1f404372</t>
+          <t>c097f2631c054985</t>
         </is>
       </c>
       <c r="B27" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:54.449023Z</t>
+          <t>2026-10-14T05:58:58.433878Z</t>
         </is>
       </c>
       <c r="C27" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T16:00:00Z</t>
+          <t>2026-10-14T09:00:00Z</t>
         </is>
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>156718</t>
+          <t>158214</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="I27" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J27" s="25" t="n"/>
@@ -9779,26 +9779,26 @@
         </is>
       </c>
       <c r="L27" s="26" t="n">
-        <v>156</v>
+        <v>-170</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>2.56</v>
+        <v>1.588235</v>
       </c>
       <c r="N27" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.62963</v>
       </c>
       <c r="O27" s="28" t="n">
-        <v>0.523645</v>
+        <v>0.591355</v>
       </c>
       <c r="P27" s="28" t="n"/>
       <c r="Q27" s="28" t="n">
-        <v>0.13302</v>
+        <v>-0.038275</v>
       </c>
       <c r="R27" s="26" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
       <c r="AD27" s="24" t="n"/>
       <c r="AE27" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
         </is>
       </c>
       <c r="AF27" s="31" t="inlineStr">
@@ -9839,7 +9839,7 @@
       <c r="AJ27" s="31" t="n"/>
       <c r="AK27" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL27" s="26" t="n">
@@ -9847,7 +9847,7 @@
       </c>
       <c r="AM27" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN27" s="24" t="inlineStr">
@@ -9857,22 +9857,22 @@
       </c>
       <c r="AO27" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP27" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="AQ27" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="AR27" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Kalmychata</t>
         </is>
       </c>
       <c r="AS27" s="24" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="BA27" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BB27" s="24" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="BD27" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BE27" s="24" t="inlineStr">
@@ -9940,7 +9940,7 @@
       </c>
       <c r="BH27" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:32:02.017912Z</t>
+          <t>2026-10-14T05:53:14.998361Z</t>
         </is>
       </c>
       <c r="BI27" s="24" t="inlineStr">
@@ -9950,13 +9950,13 @@
       </c>
       <c r="BJ27" s="25" t="n"/>
       <c r="BK27" s="26" t="n">
-        <v>156</v>
+        <v>-170</v>
       </c>
       <c r="BL27" s="27" t="n">
-        <v>2.56</v>
+        <v>1.588235</v>
       </c>
       <c r="BM27" s="28" t="n">
-        <v>0.390625</v>
+        <v>0.62963</v>
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
@@ -9991,7 +9991,7 @@
       <c r="CR27" s="24" t="n"/>
       <c r="CS27" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT27" s="24" t="n"/>
@@ -10019,29 +10019,29 @@
       <c r="DP27" s="24" t="n"/>
       <c r="DQ27" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "salamit", "event_id": "156718", "event_start_utc": "2026-10-14T16:00:00Z", "features": {"away_elo": 1460.287151, "away_history_count": 1, "home_elo": 1488.072875, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16398": 297, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16398": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:16398": 1488.072875, "bo3:4:25478": 1460.287151}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:16398", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.476355, "home": 0.523645}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "fcd9e7bfaf0a7aef8cfe55b5174f307553eff49f6da840b15ce6cac7e8797e4a", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Kalmychata", "event_id": "158214", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1592.507792, "away_history_count": 168, "home_elo": 1488.080158, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15089": 168, "bo3:4:16398": 297}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15089": "2026-10-13T09:00:00Z", "bo3:4:16398": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:15089": 1592.507792, "bo3:4:16398": 1488.080158}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:16398", "bo3:4:15089"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.591355, "home": 0.408645}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "792be9ee076e5b22288cb5df758d4692b44c36a8a412c06212346b571186bdfc", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="24" t="inlineStr">
         <is>
-          <t>34fe36aea8d14219</t>
+          <t>a8e6152fb6d3415e</t>
         </is>
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:54.449023Z</t>
+          <t>2026-10-14T05:58:58.433878Z</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T19:00:00Z</t>
+          <t>2026-10-14T12:00:00Z</t>
         </is>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>156716</t>
+          <t>158541</t>
         </is>
       </c>
       <c r="E28" s="24" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="H28" s="24" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="I28" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J28" s="25" t="n"/>
@@ -10076,20 +10076,20 @@
         </is>
       </c>
       <c r="L28" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="N28" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="O28" s="28" t="n">
-        <v>0.5946399999999999</v>
+        <v>0.549683</v>
       </c>
       <c r="P28" s="28" t="n"/>
       <c r="Q28" s="28" t="n">
-        <v>-0.095762</v>
+        <v>-0.059692</v>
       </c>
       <c r="R28" s="26" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
       <c r="AD28" s="24" t="n"/>
       <c r="AE28" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-yb-tr-2026-10-14).</t>
         </is>
       </c>
       <c r="AF28" s="31" t="inlineStr">
@@ -10159,32 +10159,32 @@
       </c>
       <c r="AP28" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AQ28" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AR28" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Team Resilience</t>
         </is>
       </c>
       <c r="AS28" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AT28" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AU28" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Yakult Brothers</t>
         </is>
       </c>
       <c r="AV28" s="24" t="n"/>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="BA28" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BB28" s="24" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="BD28" s="24" t="inlineStr">
         <is>
-          <t>dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697</t>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
         </is>
       </c>
       <c r="BE28" s="24" t="inlineStr">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="BH28" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:33:23.747123Z</t>
+          <t>2026-10-14T05:55:09.636207Z</t>
         </is>
       </c>
       <c r="BI28" s="24" t="inlineStr">
@@ -10247,13 +10247,13 @@
       </c>
       <c r="BJ28" s="25" t="n"/>
       <c r="BK28" s="26" t="n">
-        <v>-223</v>
+        <v>-156</v>
       </c>
       <c r="BL28" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.641026</v>
       </c>
       <c r="BM28" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.609375</v>
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
@@ -10316,7 +10316,898 @@
       <c r="DP28" s="24" t="n"/>
       <c r="DQ28" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "dc027529e76ab16bef8ea31225ca11d3fdf6385e7d78b957d3e380f789668697", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.287151, "away_history_count": 1, "home_elo": 1620.120862, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07002877626643239, "platt_slope": 0.8484442429825593, "ratings": {"bo3:4:25301": 1620.120862, "bo3:4:25478": 1460.287151}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:07.791212+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:07.791212+00:00", "probabilities": {"away": 0.40536, "home": 0.59464}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "2c88dd441710ecb8ad52dbe18df7d7bb9fa56f7788499bd04a0de2c69936ee26", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Team Resilience", "event_id": "158541", "event_start_utc": "2026-10-14T12:00:00Z", "features": {"away_elo": 1752.912205, "away_history_count": 23, "home_elo": 1689.95539, "home_history_count": 188}, "historical_source_observation_times_verified": false, "home_team": "Yakult Brothers", "inference_inputs": {"book_state": {"games_played": {"bo3:4:18586": 188, "bo3:4:23196": 23}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:18586": "2026-10-13T12:30:00Z", "bo3:4:23196": "2026-10-13T12:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:18586": 1689.95539, "bo3:4:23196": 1752.912205}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:18586", "bo3:4:23196"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.549683, "home": 0.450317}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "b0e53c870d4a1380eb6f96e8b29b1badd097645f699610f6eb160a9e1dda942b", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>83ce9365f1c8486b</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:58.433878Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>156718</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.523655</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.123655</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="n"/>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="26" t="n"/>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n"/>
+      <c r="AD29" s="24" t="n"/>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Nemiga Gaming</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:56:02.908549Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n"/>
+      <c r="BY29" s="27" t="n"/>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT29" s="24" t="n"/>
+      <c r="CU29" s="24" t="n"/>
+      <c r="CV29" s="24" t="n"/>
+      <c r="CW29" s="24" t="n"/>
+      <c r="CX29" s="24" t="n"/>
+      <c r="CY29" s="24" t="n"/>
+      <c r="CZ29" s="24" t="n"/>
+      <c r="DA29" s="24" t="n"/>
+      <c r="DB29" s="24" t="n"/>
+      <c r="DC29" s="24" t="n"/>
+      <c r="DD29" s="24" t="n"/>
+      <c r="DE29" s="24" t="n"/>
+      <c r="DF29" s="24" t="n"/>
+      <c r="DG29" s="24" t="n"/>
+      <c r="DH29" s="24" t="n"/>
+      <c r="DI29" s="24" t="n"/>
+      <c r="DJ29" s="24" t="n"/>
+      <c r="DK29" s="24" t="n"/>
+      <c r="DL29" s="24" t="n"/>
+      <c r="DM29" s="24" t="n"/>
+      <c r="DN29" s="24" t="n"/>
+      <c r="DO29" s="24" t="n"/>
+      <c r="DP29" s="24" t="n"/>
+      <c r="DQ29" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "salamit", "event_id": "156718", "event_start_utc": "2026-10-14T16:00:00Z", "features": {"away_elo": 1460.288501, "away_history_count": 1, "home_elo": 1488.080158, "home_history_count": 297}, "historical_source_observation_times_verified": false, "home_team": "Nemiga Gaming", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16398": 297, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16398": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:16398": 1488.080158, "bo3:4:25478": 1460.288501}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:16398", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.476345, "home": 0.523655}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "24a5e4b74578f47f77b530c4eb469cecd5efa6c30b455019c70d475f291f4144", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>ea4910037203439f</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:58.433878Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>156716</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.59448</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>-0.09592199999999999</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="n"/>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="26" t="n"/>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n"/>
+      <c r="AD30" s="24" t="n"/>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:56:54.523031Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n"/>
+      <c r="BY30" s="27" t="n"/>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT30" s="24" t="n"/>
+      <c r="CU30" s="24" t="n"/>
+      <c r="CV30" s="24" t="n"/>
+      <c r="CW30" s="24" t="n"/>
+      <c r="CX30" s="24" t="n"/>
+      <c r="CY30" s="24" t="n"/>
+      <c r="CZ30" s="24" t="n"/>
+      <c r="DA30" s="24" t="n"/>
+      <c r="DB30" s="24" t="n"/>
+      <c r="DC30" s="24" t="n"/>
+      <c r="DD30" s="24" t="n"/>
+      <c r="DE30" s="24" t="n"/>
+      <c r="DF30" s="24" t="n"/>
+      <c r="DG30" s="24" t="n"/>
+      <c r="DH30" s="24" t="n"/>
+      <c r="DI30" s="24" t="n"/>
+      <c r="DJ30" s="24" t="n"/>
+      <c r="DK30" s="24" t="n"/>
+      <c r="DL30" s="24" t="n"/>
+      <c r="DM30" s="24" t="n"/>
+      <c r="DN30" s="24" t="n"/>
+      <c r="DO30" s="24" t="n"/>
+      <c r="DP30" s="24" t="n"/>
+      <c r="DQ30" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.288501, "away_history_count": 1, "home_elo": 1620.074907, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:25301": 1620.074907, "bo3:4:25478": 1460.288501}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.40552, "home": 0.59448}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f63e7ddcb28fd5faf9bb7922cf0be61109ee48b76f676b6e8273dbe0a0179db", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>20af05f473b34ae2</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:58.433878Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>156803</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.607537</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>0.157087</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>99</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="n"/>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="26" t="n"/>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n"/>
+      <c r="AD31" s="24" t="n"/>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lynx-dba-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:58:16.995855Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n"/>
+      <c r="BY31" s="27" t="n"/>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT31" s="24" t="n"/>
+      <c r="CU31" s="24" t="n"/>
+      <c r="CV31" s="24" t="n"/>
+      <c r="CW31" s="24" t="n"/>
+      <c r="CX31" s="24" t="n"/>
+      <c r="CY31" s="24" t="n"/>
+      <c r="CZ31" s="24" t="n"/>
+      <c r="DA31" s="24" t="n"/>
+      <c r="DB31" s="24" t="n"/>
+      <c r="DC31" s="24" t="n"/>
+      <c r="DD31" s="24" t="n"/>
+      <c r="DE31" s="24" t="n"/>
+      <c r="DF31" s="24" t="n"/>
+      <c r="DG31" s="24" t="n"/>
+      <c r="DH31" s="24" t="n"/>
+      <c r="DI31" s="24" t="n"/>
+      <c r="DJ31" s="24" t="n"/>
+      <c r="DK31" s="24" t="n"/>
+      <c r="DL31" s="24" t="n"/>
+      <c r="DM31" s="24" t="n"/>
+      <c r="DN31" s="24" t="n"/>
+      <c r="DO31" s="24" t="n"/>
+      <c r="DP31" s="24" t="n"/>
+      <c r="DQ31" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Dawn Bulls", "event_id": "156803", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1620.074907, "away_history_count": 6, "home_elo": 1740.227749, "home_history_count": 186}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:19913": 186, "bo3:4:25301": 6}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:19913": "2026-10-13T07:00:00Z", "bo3:4:25301": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:19913": 1740.227749, "bo3:4:25301": 1620.074907}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:19913", "bo3:4:25301"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.392463, "home": 0.607537}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f91224b5f1040bd11c25b0422ef87b0b2899559b8a5d935ff122f45428a9806", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/dota2/research.xlsx
+++ b/data/sports/dota2/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ31" headerRowCount="1">
-  <autoFilter ref="A1:DQ31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ36" headerRowCount="1">
+  <autoFilter ref="A1:DQ36"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$31)</f>
+        <f>COUNTA('Picks'!$A$2:$A$36)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$36,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")+COUNTIFS('Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$31,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$36,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")/(COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"win")+COUNTIFS('Picks'!$BX$2:$BX$31,"&gt;0",'Picks'!$V$2:$V$31,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")/(COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"win")+COUNTIFS('Picks'!$BX$2:$BX$36,"&gt;0",'Picks'!$V$2:$V$36,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$31)/SUM('Picks'!$BX$2:$BX$31),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$36)/SUM('Picks'!$BX$2:$BX$36),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$31)</f>
+        <f>SUM('Picks'!$BY$2:$BY$36)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$31,"&lt;&gt;",'Picks'!$AB$2:$AB$31),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$36,"&lt;&gt;",'Picks'!$AB$2:$AB$36),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$36,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$31,'Picks'!$AM$2:$AM$31,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$36,'Picks'!$AM$2:$AM$36,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A14,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A14,'Picks'!$U$2:$U$36,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A15,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A15,'Picks'!$U$2:$U$36,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled",'Picks'!$V$2:$V$31,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled",'Picks'!$V$2:$V$36,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$31,'Picks'!$H$2:$H$31,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$36,'Picks'!$H$2:$H$36,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$31,'Picks'!$H$2:$H$31,$A16,'Picks'!$U$2:$U$31,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$36,'Picks'!$H$2:$H$36,$A16,'Picks'!$U$2:$U$36,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ31"/>
+  <dimension ref="A1:DQ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9512,18 +9512,32 @@
       </c>
       <c r="U26" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V26" s="24" t="n"/>
-      <c r="W26" s="26" t="n"/>
-      <c r="X26" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y26" s="25" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n"/>
-      <c r="AD26" s="24" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:16:10.151842Z</t>
+        </is>
+      </c>
       <c r="AE26" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=tsc-dota2-nemiga-kalmy-2026-10-14-tot-2pt5).</t>
@@ -9536,7 +9550,7 @@
       </c>
       <c r="AG26" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH26" s="24" t="n"/>
@@ -9807,18 +9821,38 @@
       </c>
       <c r="U27" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V27" s="24" t="n"/>
-      <c r="W27" s="26" t="n"/>
-      <c r="X27" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y27" s="25" t="n"/>
-      <c r="Z27" s="26" t="n"/>
-      <c r="AA27" s="28" t="n"/>
-      <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n"/>
-      <c r="AD27" s="24" t="n"/>
+      <c r="Z27" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="AA27" s="28" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB27" s="28" t="n">
+        <v>0.00037</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:16:13.126559Z</t>
+        </is>
+      </c>
       <c r="AE27" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6300 (market_slug=aec-dota2-nemiga-kalmy-2026-10-14).</t>
@@ -9961,8 +9995,12 @@
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
       <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
-      <c r="BR27" s="28" t="n"/>
+      <c r="BQ27" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BR27" s="28" t="n">
+        <v>0.63</v>
+      </c>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
       <c r="BU27" s="25" t="n"/>
@@ -10104,18 +10142,38 @@
       </c>
       <c r="U28" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V28" s="24" t="n"/>
-      <c r="W28" s="26" t="n"/>
-      <c r="X28" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y28" s="25" t="n"/>
-      <c r="Z28" s="26" t="n"/>
-      <c r="AA28" s="28" t="n"/>
-      <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n"/>
-      <c r="AD28" s="24" t="n"/>
+      <c r="Z28" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA28" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB28" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC28" s="30" t="n">
+        <v>0.641</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:16:16.355753Z</t>
+        </is>
+      </c>
       <c r="AE28" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-dota2-yb-tr-2026-10-14).</t>
@@ -10258,8 +10316,12 @@
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
       <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
-      <c r="BR28" s="28" t="n"/>
+      <c r="BQ28" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR28" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
       <c r="BU28" s="25" t="n"/>
@@ -10401,18 +10463,38 @@
       </c>
       <c r="U29" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V29" s="24" t="n"/>
-      <c r="W29" s="26" t="n"/>
-      <c r="X29" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y29" s="25" t="n"/>
-      <c r="Z29" s="26" t="n"/>
-      <c r="AA29" s="28" t="n"/>
-      <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n"/>
-      <c r="AD29" s="24" t="n"/>
+      <c r="Z29" s="26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA29" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AB29" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:35.215421Z</t>
+        </is>
+      </c>
       <c r="AE29" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-nemiga-sala-2026-10-14).</t>
@@ -10425,7 +10507,7 @@
       </c>
       <c r="AG29" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH29" s="24" t="n"/>
@@ -10555,8 +10637,12 @@
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
       <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
-      <c r="BR29" s="28" t="n"/>
+      <c r="BQ29" s="27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BR29" s="28" t="n">
+        <v>0.4</v>
+      </c>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
       <c r="BU29" s="25" t="n"/>
@@ -10620,22 +10706,22 @@
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="24" t="inlineStr">
         <is>
-          <t>ea4910037203439f</t>
+          <t>2be483f49c9540f7</t>
         </is>
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:58:58.433878Z</t>
+          <t>2026-10-14T16:27:13.864206Z</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T19:00:00Z</t>
+          <t>2026-10-14T17:00:00Z</t>
         </is>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>156716</t>
+          <t>159104</t>
         </is>
       </c>
       <c r="E30" s="24" t="inlineStr">
@@ -10645,12 +10731,12 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="H30" s="24" t="inlineStr">
@@ -10660,7 +10746,7 @@
       </c>
       <c r="I30" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J30" s="25" t="n"/>
@@ -10670,20 +10756,20 @@
         </is>
       </c>
       <c r="L30" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="N30" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="O30" s="28" t="n">
-        <v>0.59448</v>
+        <v>0.562152</v>
       </c>
       <c r="P30" s="28" t="n"/>
       <c r="Q30" s="28" t="n">
-        <v>-0.09592199999999999</v>
+        <v>-0.137548</v>
       </c>
       <c r="R30" s="26" t="n">
         <v>0</v>
@@ -10698,21 +10784,41 @@
       </c>
       <c r="U30" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V30" s="24" t="n"/>
-      <c r="W30" s="26" t="n"/>
-      <c r="X30" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y30" s="25" t="n"/>
-      <c r="Z30" s="26" t="n"/>
-      <c r="AA30" s="28" t="n"/>
-      <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n"/>
-      <c r="AD30" s="24" t="n"/>
+      <c r="Z30" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="AA30" s="28" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB30" s="28" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:46.531228Z</t>
+        </is>
+      </c>
       <c r="AE30" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-dota2-nge-hkr-2026-10-14).</t>
         </is>
       </c>
       <c r="AF30" s="31" t="inlineStr">
@@ -10753,32 +10859,32 @@
       </c>
       <c r="AP30" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="AQ30" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="AR30" s="24" t="inlineStr">
         <is>
-          <t>salamit</t>
+          <t>Hokori</t>
         </is>
       </c>
       <c r="AS30" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="AT30" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="AU30" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>New Growth</t>
         </is>
       </c>
       <c r="AV30" s="24" t="n"/>
@@ -10796,7 +10902,7 @@
       </c>
       <c r="BA30" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BB30" s="24" t="inlineStr">
@@ -10811,7 +10917,7 @@
       </c>
       <c r="BD30" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BE30" s="24" t="inlineStr">
@@ -10831,7 +10937,7 @@
       </c>
       <c r="BH30" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:56:54.523031Z</t>
+          <t>2026-10-14T16:25:51.391990Z</t>
         </is>
       </c>
       <c r="BI30" s="24" t="inlineStr">
@@ -10841,19 +10947,23 @@
       </c>
       <c r="BJ30" s="25" t="n"/>
       <c r="BK30" s="26" t="n">
-        <v>-223</v>
+        <v>-233</v>
       </c>
       <c r="BL30" s="27" t="n">
-        <v>1.44843</v>
+        <v>1.429185</v>
       </c>
       <c r="BM30" s="28" t="n">
-        <v>0.690402</v>
+        <v>0.6997</v>
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
       <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
-      <c r="BR30" s="28" t="n"/>
+      <c r="BQ30" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BR30" s="28" t="n">
+        <v>0.76</v>
+      </c>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
       <c r="BU30" s="25" t="n"/>
@@ -10910,29 +11020,29 @@
       <c r="DP30" s="24" t="n"/>
       <c r="DQ30" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.288501, "away_history_count": 1, "home_elo": 1620.074907, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:25301": 1620.074907, "bo3:4:25478": 1460.288501}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.40552, "home": 0.59448}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f63e7ddcb28fd5faf9bb7922cf0be61109ee48b76f676b6e8273dbe0a0179db", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "Hokori", "event_id": "159104", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1587.595589, "away_history_count": 93, "home_elo": 1511.739528, "home_history_count": 15}, "historical_source_observation_times_verified": false, "home_team": "New Growth", "inference_inputs": {"book_state": {"games_played": {"bo3:4:15828": 93, "bo3:4:22378": 15}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:15828": "2026-10-13T17:10:00Z", "bo3:4:22378": "2026-10-13T17:15:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:15828": 1587.595589, "bo3:4:22378": 1511.739528}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:22378", "bo3:4:15828"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.562152, "home": 0.437848}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d1c9ac18453b9cbab360dfe4e5be811f611b79e9b9bb5035e88ea7fe1674bfe0", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="24" t="inlineStr">
         <is>
-          <t>20af05f473b34ae2</t>
+          <t>e0917ecfe396428d</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:58:58.433878Z</t>
+          <t>2026-10-14T16:27:13.864206Z</t>
         </is>
       </c>
       <c r="C31" s="24" t="inlineStr">
         <is>
-          <t>2026-10-15T10:00:00Z</t>
+          <t>2026-10-14T17:00:00Z</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>156803</t>
+          <t>159527</t>
         </is>
       </c>
       <c r="E31" s="24" t="inlineStr">
@@ -10942,12 +11052,12 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
@@ -10957,7 +11067,7 @@
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J31" s="25" t="n"/>
@@ -10967,26 +11077,26 @@
         </is>
       </c>
       <c r="L31" s="26" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.4</v>
       </c>
       <c r="O31" s="28" t="n">
-        <v>0.607537</v>
+        <v>0.5145110000000001</v>
       </c>
       <c r="P31" s="28" t="n"/>
       <c r="Q31" s="28" t="n">
-        <v>0.157087</v>
+        <v>0.114511</v>
       </c>
       <c r="R31" s="26" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -10995,21 +11105,41 @@
       </c>
       <c r="U31" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V31" s="24" t="n"/>
-      <c r="W31" s="26" t="n"/>
-      <c r="X31" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y31" s="25" t="n"/>
-      <c r="Z31" s="26" t="n"/>
-      <c r="AA31" s="28" t="n"/>
-      <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n"/>
-      <c r="AD31" s="24" t="n"/>
+      <c r="Z31" s="26" t="n">
+        <v>-400</v>
+      </c>
+      <c r="AA31" s="28" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB31" s="28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC31" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:47.682370Z</t>
+        </is>
+      </c>
       <c r="AE31" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lynx-dba-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-dota2-sky-rl-2026-10-14).</t>
         </is>
       </c>
       <c r="AF31" s="31" t="inlineStr">
@@ -11019,7 +11149,7 @@
       </c>
       <c r="AG31" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH31" s="24" t="n"/>
@@ -11050,32 +11180,32 @@
       </c>
       <c r="AP31" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="AQ31" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="AR31" s="24" t="inlineStr">
         <is>
-          <t>Dawn Bulls</t>
+          <t>Rottweilas Latam</t>
         </is>
       </c>
       <c r="AS31" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="AT31" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="AU31" s="24" t="inlineStr">
         <is>
-          <t>Team Lynx</t>
+          <t>Skyreavers</t>
         </is>
       </c>
       <c r="AV31" s="24" t="n"/>
@@ -11093,7 +11223,7 @@
       </c>
       <c r="BA31" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BB31" s="24" t="inlineStr">
@@ -11108,7 +11238,7 @@
       </c>
       <c r="BD31" s="24" t="inlineStr">
         <is>
-          <t>fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd</t>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
         </is>
       </c>
       <c r="BE31" s="24" t="inlineStr">
@@ -11128,7 +11258,7 @@
       </c>
       <c r="BH31" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:58:16.995855Z</t>
+          <t>2026-10-14T16:26:32.931088Z</t>
         </is>
       </c>
       <c r="BI31" s="24" t="inlineStr">
@@ -11138,19 +11268,23 @@
       </c>
       <c r="BJ31" s="25" t="n"/>
       <c r="BK31" s="26" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="BL31" s="27" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="BM31" s="28" t="n">
-        <v>0.45045</v>
+        <v>0.4</v>
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
       <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
-      <c r="BR31" s="28" t="n"/>
+      <c r="BQ31" s="27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BR31" s="28" t="n">
+        <v>0.8</v>
+      </c>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
       <c r="BU31" s="25" t="n"/>
@@ -11207,7 +11341,1530 @@
       <c r="DP31" s="24" t="n"/>
       <c r="DQ31" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "fc46e0136357aa43869ef4ced7c0aa68d9788a5409ce876dbdac1283872f80fd", "away_team": "Dawn Bulls", "event_id": "156803", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1620.074907, "away_history_count": 6, "home_elo": 1740.227749, "home_history_count": 186}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:19913": 186, "bo3:4:25301": 6}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:19913": "2026-10-13T07:00:00Z", "bo3:4:25301": "2026-10-13T16:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.07036763852883177, "platt_slope": 0.8490234145215234, "ratings": {"bo3:4:19913": 1740.227749, "bo3:4:25301": 1620.074907}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:14.083136+00:00", "team_ids": ["bo3:4:19913", "bo3:4:25301"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:14.083136+00:00", "probabilities": {"away": 0.392463, "home": 0.607537}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9f91224b5f1040bd11c25b0422ef87b0b2899559b8a5d935ff122f45428a9806", "sport": "DOTA2"}</t>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "Rottweilas Latam", "event_id": "159527", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1555.776918, "away_history_count": 15, "home_elo": 1522.384807, "home_history_count": 5}, "historical_source_observation_times_verified": false, "home_team": "Skyreavers", "inference_inputs": {"book_state": {"games_played": {"bo3:4:22288": 15, "bo3:4:25468": 5}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:22288": "2026-10-13T21:00:00Z", "bo3:4:25468": "2026-10-13T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:22288": 1555.776918, "bo3:4:25468": 1522.384807}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:25468", "bo3:4:22288"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.514511, "home": 0.485489}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "53e21587e49ce07031479c6ea4c0f7d59d4a6641af182747482efe9dd33de1b1", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>bcd57d1678884086</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:27:13.864206Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>159889</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.56987</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>0.160034</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:49.037405Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-dota2-bot-kt-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Korb3n Team</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>by Owl Team</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:26:33.015972Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n"/>
+      <c r="BY32" s="27" t="n"/>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT32" s="24" t="n"/>
+      <c r="CU32" s="24" t="n"/>
+      <c r="CV32" s="24" t="n"/>
+      <c r="CW32" s="24" t="n"/>
+      <c r="CX32" s="24" t="n"/>
+      <c r="CY32" s="24" t="n"/>
+      <c r="CZ32" s="24" t="n"/>
+      <c r="DA32" s="24" t="n"/>
+      <c r="DB32" s="24" t="n"/>
+      <c r="DC32" s="24" t="n"/>
+      <c r="DD32" s="24" t="n"/>
+      <c r="DE32" s="24" t="n"/>
+      <c r="DF32" s="24" t="n"/>
+      <c r="DG32" s="24" t="n"/>
+      <c r="DH32" s="24" t="n"/>
+      <c r="DI32" s="24" t="n"/>
+      <c r="DJ32" s="24" t="n"/>
+      <c r="DK32" s="24" t="n"/>
+      <c r="DL32" s="24" t="n"/>
+      <c r="DM32" s="24" t="n"/>
+      <c r="DN32" s="24" t="n"/>
+      <c r="DO32" s="24" t="n"/>
+      <c r="DP32" s="24" t="n"/>
+      <c r="DQ32" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "Korb3n Team", "event_id": "159889", "event_start_utc": "2026-10-14T17:00:00Z", "features": {"away_elo": 1413.038012, "away_history_count": 4, "home_elo": 1622.517552, "home_history_count": 15}, "historical_source_observation_times_verified": false, "home_team": "by Owl Team", "inference_inputs": {"book_state": {"games_played": {"bo3:4:20838": 4, "bo3:4:21660": 15}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:20838": "2025-06-05T18:15:00Z", "bo3:4:21660": "2025-11-30T14:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:20838": 1413.038012, "bo3:4:21660": 1622.517552}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:21660", "bo3:4:20838"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.43013, "home": 0.56987}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "d4e2a64a9f5668351842c1563ecc563be1b30fa530535fc1eb116755d6aad808", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>7661844d13214c3b</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:27:13.864206Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T19:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>156716</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.5931959999999999</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>-0.097206</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="AA33" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB33" s="28" t="n">
+        <v>-0.000402</v>
+      </c>
+      <c r="AC33" s="30" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:03:50.252949Z</t>
+        </is>
+      </c>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=aec-dota2-dba-sala-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>salamit</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:26:43.456466Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BR33" s="28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT33" s="24" t="n"/>
+      <c r="CU33" s="24" t="n"/>
+      <c r="CV33" s="24" t="n"/>
+      <c r="CW33" s="24" t="n"/>
+      <c r="CX33" s="24" t="n"/>
+      <c r="CY33" s="24" t="n"/>
+      <c r="CZ33" s="24" t="n"/>
+      <c r="DA33" s="24" t="n"/>
+      <c r="DB33" s="24" t="n"/>
+      <c r="DC33" s="24" t="n"/>
+      <c r="DD33" s="24" t="n"/>
+      <c r="DE33" s="24" t="n"/>
+      <c r="DF33" s="24" t="n"/>
+      <c r="DG33" s="24" t="n"/>
+      <c r="DH33" s="24" t="n"/>
+      <c r="DI33" s="24" t="n"/>
+      <c r="DJ33" s="24" t="n"/>
+      <c r="DK33" s="24" t="n"/>
+      <c r="DL33" s="24" t="n"/>
+      <c r="DM33" s="24" t="n"/>
+      <c r="DN33" s="24" t="n"/>
+      <c r="DO33" s="24" t="n"/>
+      <c r="DP33" s="24" t="n"/>
+      <c r="DQ33" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a26d1a2618ded7e8f22b4b2c5138289c1c878e083c3b9d36683afd24812292e0", "away_team": "salamit", "event_id": "156716", "event_start_utc": "2026-10-14T19:00:00Z", "features": {"away_elo": 1460.359665, "away_history_count": 1, "home_elo": 1619.975066, "home_history_count": 6}, "historical_source_observation_times_verified": false, "home_team": "Dawn Bulls", "inference_inputs": {"book_state": {"games_played": {"bo3:4:25301": 6, "bo3:4:25478": 1}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:25301": "2026-10-13T16:00:00Z", "bo3:4:25478": "2026-10-12T13:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06909602886851295, "platt_slope": 0.8410344295425396, "ratings": {"bo3:4:25301": 1619.975066, "bo3:4:25478": 1460.359665}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T16:25:51.279063+00:00", "team_ids": ["bo3:4:25301", "bo3:4:25478"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T16:25:51.279063+00:00", "probabilities": {"away": 0.406804, "home": 0.593196}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "cabcc8a699a98345988ad0f64096ec22f1d9b9d311724c52f265d49816451015", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>be3a94d2a7f7405c</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:57.652722Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>156063</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.527991</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.137366</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>89</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3900 (market_slug=aec-dota2-xctn-rb-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Royal Bear</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Execration</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:53.140829Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT34" s="24" t="n"/>
+      <c r="CU34" s="24" t="n"/>
+      <c r="CV34" s="24" t="n"/>
+      <c r="CW34" s="24" t="n"/>
+      <c r="CX34" s="24" t="n"/>
+      <c r="CY34" s="24" t="n"/>
+      <c r="CZ34" s="24" t="n"/>
+      <c r="DA34" s="24" t="n"/>
+      <c r="DB34" s="24" t="n"/>
+      <c r="DC34" s="24" t="n"/>
+      <c r="DD34" s="24" t="n"/>
+      <c r="DE34" s="24" t="n"/>
+      <c r="DF34" s="24" t="n"/>
+      <c r="DG34" s="24" t="n"/>
+      <c r="DH34" s="24" t="n"/>
+      <c r="DI34" s="24" t="n"/>
+      <c r="DJ34" s="24" t="n"/>
+      <c r="DK34" s="24" t="n"/>
+      <c r="DL34" s="24" t="n"/>
+      <c r="DM34" s="24" t="n"/>
+      <c r="DN34" s="24" t="n"/>
+      <c r="DO34" s="24" t="n"/>
+      <c r="DP34" s="24" t="n"/>
+      <c r="DQ34" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870", "away_team": "Royal Bear", "event_id": "156063", "event_start_utc": "2026-10-15T04:00:00Z", "features": {"away_elo": 1565.005066, "away_history_count": 2, "home_elo": 1620.77125, "home_history_count": 232}, "historical_source_observation_times_verified": false, "home_team": "Execration", "inference_inputs": {"book_state": {"games_played": {"bo3:4:16710": 232, "bo3:4:25439": 2}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:16710": "2026-09-13T05:45:00Z", "bo3:4:25439": "2026-10-10T08:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0741677632303944, "platt_slope": 0.8370812307603834, "ratings": {"bo3:4:16710": 1620.77125, "bo3:4:25439": 1565.005066}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.820014+00:00", "team_ids": ["bo3:4:16710", "bo3:4:25439"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.820014+00:00", "probabilities": {"away": 0.472009, "home": 0.527991}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "21e684090db0fc15459d72e5adb631b9021f69f3e924847f36be1bc1730bee91", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>68e42885fd4d4714</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:57.652722Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>156799</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.6493910000000001</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>0.07857599999999999</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5700 (market_slug=aec-dota2-db-tke-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Team Kinetix</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Direborn</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:46:53.205469Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT35" s="24" t="n"/>
+      <c r="CU35" s="24" t="n"/>
+      <c r="CV35" s="24" t="n"/>
+      <c r="CW35" s="24" t="n"/>
+      <c r="CX35" s="24" t="n"/>
+      <c r="CY35" s="24" t="n"/>
+      <c r="CZ35" s="24" t="n"/>
+      <c r="DA35" s="24" t="n"/>
+      <c r="DB35" s="24" t="n"/>
+      <c r="DC35" s="24" t="n"/>
+      <c r="DD35" s="24" t="n"/>
+      <c r="DE35" s="24" t="n"/>
+      <c r="DF35" s="24" t="n"/>
+      <c r="DG35" s="24" t="n"/>
+      <c r="DH35" s="24" t="n"/>
+      <c r="DI35" s="24" t="n"/>
+      <c r="DJ35" s="24" t="n"/>
+      <c r="DK35" s="24" t="n"/>
+      <c r="DL35" s="24" t="n"/>
+      <c r="DM35" s="24" t="n"/>
+      <c r="DN35" s="24" t="n"/>
+      <c r="DO35" s="24" t="n"/>
+      <c r="DP35" s="24" t="n"/>
+      <c r="DQ35" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870", "away_team": "Team Kinetix", "event_id": "156799", "event_start_utc": "2026-10-15T04:00:00Z", "features": {"away_elo": 1454.932244, "away_history_count": 17, "home_elo": 1597.368763, "home_history_count": 40}, "historical_source_observation_times_verified": false, "home_team": "Direborn", "inference_inputs": {"book_state": {"games_played": {"bo3:4:24344": 40, "bo3:4:25225": 17}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:24344": "2026-10-08T03:10:00Z", "bo3:4:25225": "2026-10-12T08:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0741677632303944, "platt_slope": 0.8370812307603834, "ratings": {"bo3:4:24344": 1597.368763, "bo3:4:25225": 1454.932244}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.820014+00:00", "team_ids": ["bo3:4:24344", "bo3:4:25225"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.820014+00:00", "probabilities": {"away": 0.350609, "home": 0.649391}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "9aa03fcfb2d0ec6dca89faef6ba9ac3db646dcd5a3c5249be6a09f2755ed94cd", "sport": "DOTA2"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>79cbf26d3c3d49c4</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:57.652722Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>156803</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>DOTA2</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.612465</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>0.162015</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-dota2-lynx-dba-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Dawn Bulls</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Team Lynx</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T22:48:05.177623Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>122</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT36" s="24" t="n"/>
+      <c r="CU36" s="24" t="n"/>
+      <c r="CV36" s="24" t="n"/>
+      <c r="CW36" s="24" t="n"/>
+      <c r="CX36" s="24" t="n"/>
+      <c r="CY36" s="24" t="n"/>
+      <c r="CZ36" s="24" t="n"/>
+      <c r="DA36" s="24" t="n"/>
+      <c r="DB36" s="24" t="n"/>
+      <c r="DC36" s="24" t="n"/>
+      <c r="DD36" s="24" t="n"/>
+      <c r="DE36" s="24" t="n"/>
+      <c r="DF36" s="24" t="n"/>
+      <c r="DG36" s="24" t="n"/>
+      <c r="DH36" s="24" t="n"/>
+      <c r="DI36" s="24" t="n"/>
+      <c r="DJ36" s="24" t="n"/>
+      <c r="DK36" s="24" t="n"/>
+      <c r="DL36" s="24" t="n"/>
+      <c r="DM36" s="24" t="n"/>
+      <c r="DN36" s="24" t="n"/>
+      <c r="DO36" s="24" t="n"/>
+      <c r="DP36" s="24" t="n"/>
+      <c r="DQ36" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "158823ce1a587d2f3671a0256c3ba7ba544c89560e738394a181423449115870", "away_team": "Dawn Bulls", "event_id": "156803", "event_start_utc": "2026-10-15T10:00:00Z", "features": {"away_elo": 1640.18007, "away_history_count": 7, "home_elo": 1758.623049, "home_history_count": 188}, "historical_source_observation_times_verified": false, "home_team": "Team Lynx", "inference_inputs": {"book_state": {"games_played": {"bo3:4:19913": 188, "bo3:4:25301": 7}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:4:19913": "2026-10-14T10:00:00Z", "bo3:4:25301": "2026-10-14T19:10:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0741677632303944, "platt_slope": 0.8370812307603834, "ratings": {"bo3:4:19913": 1758.623049, "bo3:4:25301": 1640.18007}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.820014+00:00", "team_ids": ["bo3:4:19913", "bo3:4:25301"]}, "market_type": "moneyline", "model_version": "dota2-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.820014+00:00", "probabilities": {"away": 0.387535, "home": 0.612465}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "6f823458a4506198d775b496a2f575e24740130115de5ca82ae946e9b2b115a0", "sport": "DOTA2"}</t>
         </is>
       </c>
     </row>
